--- a/Server/NewServer/bin/commonconfig/setting/guild_achievement.xlsx
+++ b/Server/NewServer/bin/commonconfig/setting/guild_achievement.xlsx
@@ -32,7 +32,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者</t>
+          <t>Author</t>
         </r>
         <r>
           <rPr>
@@ -58,7 +58,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者</t>
+          <t>Author</t>
         </r>
         <r>
           <rPr>
@@ -100,7 +100,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -111,7 +111,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-取值范围</t>
+Allowed range</t>
         </r>
         <r>
           <rPr>
@@ -134,7 +134,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -166,7 +166,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -177,7 +177,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-取值范围</t>
+Allowed range</t>
         </r>
         <r>
           <rPr>
@@ -200,7 +200,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -232,7 +232,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -243,7 +243,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-取值范围</t>
+Allowed range</t>
         </r>
         <r>
           <rPr>
@@ -266,7 +266,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -298,7 +298,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -309,7 +309,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-取值范围</t>
+Allowed range</t>
         </r>
         <r>
           <rPr>
@@ -333,7 +333,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者</t>
+          <t>Author</t>
         </r>
         <r>
           <rPr>
@@ -386,7 +386,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -424,7 +424,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者</t>
+          <t>Author</t>
         </r>
         <r>
           <rPr>
